--- a/data/trans_dic/IP37-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han trabajado anteriormente</t>
+          <t>Adultos que han trabajado anteriormente (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,46; 74,15</t>
+          <t>52,36; 75,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,44; 86,82</t>
+          <t>72,33; 86,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66,69; 83,65</t>
+          <t>67,68; 83,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,77; 90,29</t>
+          <t>59,27; 90,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,21; 72,1</t>
+          <t>51,13; 72,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,06; 86,6</t>
+          <t>72,68; 86,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,06; 81,91</t>
+          <t>64,37; 82,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,2; 88,01</t>
+          <t>55,28; 87,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,98; 69,92</t>
+          <t>54,84; 70,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74,26; 84,48</t>
+          <t>74,15; 84,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69,09; 80,83</t>
+          <t>68,18; 80,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,62; 84,6</t>
+          <t>62,68; 84,65</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,14; 73,57</t>
+          <t>58,18; 74,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,39; 85,56</t>
+          <t>72,51; 85,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,08; 82,55</t>
+          <t>69,1; 82,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,6; 83,41</t>
+          <t>63,96; 83,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,92; 74,01</t>
+          <t>60,11; 74,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,16; 79,07</t>
+          <t>66,34; 78,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,85; 81,61</t>
+          <t>70,08; 82,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,77; 88,76</t>
+          <t>70,34; 88,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61,95; 72,6</t>
+          <t>61,58; 72,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71,84; 80,53</t>
+          <t>71,66; 80,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71,64; 80,95</t>
+          <t>71,41; 80,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>70,68; 84,65</t>
+          <t>71,31; 84,18</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45,38; 64,47</t>
+          <t>45,33; 63,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,96; 86,95</t>
+          <t>71,54; 86,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,86; 86,86</t>
+          <t>73,86; 87,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,97; 77,15</t>
+          <t>53,54; 76,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,6; 77,74</t>
+          <t>58,24; 78,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,35; 77,0</t>
+          <t>61,11; 77,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,99; 80,6</t>
+          <t>65,8; 80,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,64; 75,67</t>
+          <t>53,48; 75,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,41; 68,03</t>
+          <t>54,25; 67,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,93; 79,86</t>
+          <t>68,37; 80,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,0; 82,31</t>
+          <t>72,37; 82,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,67; 72,64</t>
+          <t>57,36; 72,98</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,8; 66,5</t>
+          <t>49,02; 65,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,58; 75,22</t>
+          <t>59,63; 74,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,38; 78,9</t>
+          <t>62,9; 79,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,11; 85,07</t>
+          <t>57,3; 84,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,61; 64,24</t>
+          <t>48,33; 64,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,36; 78,21</t>
+          <t>64,02; 78,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,6; 75,46</t>
+          <t>58,89; 75,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56,67; 74,5</t>
+          <t>56,36; 75,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,62; 62,14</t>
+          <t>51,18; 63,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64,07; 74,47</t>
+          <t>64,18; 75,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63,95; 75,96</t>
+          <t>63,97; 75,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,34; 78,09</t>
+          <t>60,43; 78,34</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>56,86; 66,29</t>
+          <t>56,54; 65,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,46; 80,34</t>
+          <t>73,19; 80,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,36; 79,79</t>
+          <t>72,55; 79,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,64; 79,49</t>
+          <t>63,07; 79,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,76; 67,42</t>
+          <t>59,07; 67,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,75; 76,96</t>
+          <t>69,99; 76,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,34; 76,82</t>
+          <t>69,66; 77,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,93; 75,68</t>
+          <t>63,54; 75,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58,98; 65,36</t>
+          <t>59,08; 65,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72,56; 77,35</t>
+          <t>72,26; 77,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,04; 77,25</t>
+          <t>72,01; 77,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,78; 75,57</t>
+          <t>65,86; 75,95</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han trabajado anteriormente (tasa de respuesta: 99,71%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>27218</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67590</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>54722</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13475</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34951</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>66253</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>44657</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>62169</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>133843</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>99379</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>26325</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>22274; 31981</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>61209; 73607</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48695; 60159</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10392; 15779</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28975; 41014</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>60174; 71608</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>38954; 49936</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>9671; 15246</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>54404; 69952</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>124139; 141136</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>90314; 106837</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>21955; 29649</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>69559</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>104160</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78182</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37370</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72765</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>105394</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95965</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>50550</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>142324</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>209554</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>174147</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>87920</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>60500; 77061</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>94656; 111107</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>70526; 84679</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>32207; 42240</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>64849; 79943</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>95590; 113335</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>88036; 103160</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>43708; 55177</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>130477; 152690</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>196786; 220863</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>162581; 183741</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>80218; 94696</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>39754</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66440</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>77857</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43197</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39331</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>56021</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70264</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>42299</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>79085</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>122461</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148121</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>85496</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>32675; 46029</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59561; 72360</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70689; 83753</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35336; 50673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>33316; 44788</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>49264; 62776</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>63013; 77505</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>34388; 48699</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>70142; 87607</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>112043; 131639</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>138571; 157879</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>74745; 95091</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>47770</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>61366</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66053</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>86414</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53952</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76554</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>57590</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>74266</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>101721</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>137921</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>123643</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>160681</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>40629; 54474</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54063; 67906</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>58253; 73268</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>70918; 104731</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>45997; 61838</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>68626; 83664</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>50027; 64460</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>63404; 84424</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>91132; 112566</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>126987; 149219</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>113589; 133583</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>142777; 185074</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>184301</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>299556</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>276814</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>180457</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>200999</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>304222</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>179964</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>385300</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>603778</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>545289</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>360421</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>170456; 197088</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>284784; 312239</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>262856; 288726</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>162495; 204839</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>187220; 214065</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>290227; 317646</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>255559; 283291</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>162932; 192773</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>365387; 404206</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>580782; 623064</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>525049; 563719</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>338564; 390416</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP37-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,36; 75,18</t>
+          <t>51,89; 75,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,33; 86,98</t>
+          <t>71,68; 86,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,68; 83,61</t>
+          <t>67,14; 83,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,27; 90,0</t>
+          <t>58,66; 91,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,13; 72,37</t>
+          <t>51,17; 71,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,68; 86,49</t>
+          <t>70,16; 86,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,37; 82,52</t>
+          <t>64,36; 81,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,28; 87,15</t>
+          <t>53,03; 86,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,84; 70,51</t>
+          <t>54,76; 70,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74,15; 84,3</t>
+          <t>75,06; 84,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68,18; 80,65</t>
+          <t>68,58; 80,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,68; 84,65</t>
+          <t>62,52; 85,28</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,18; 74,1</t>
+          <t>59,59; 74,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,51; 85,11</t>
+          <t>73,14; 84,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,1; 82,97</t>
+          <t>70,11; 82,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,96; 83,89</t>
+          <t>62,99; 83,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,11; 74,1</t>
+          <t>60,29; 74,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,34; 78,66</t>
+          <t>66,92; 79,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,08; 82,13</t>
+          <t>69,78; 82,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>70,34; 88,8</t>
+          <t>71,18; 88,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61,58; 72,06</t>
+          <t>61,15; 71,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71,66; 80,42</t>
+          <t>71,78; 80,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71,41; 80,7</t>
+          <t>72,04; 80,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,31; 84,18</t>
+          <t>71,19; 84,01</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45,33; 63,86</t>
+          <t>45,8; 64,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,54; 86,91</t>
+          <t>72,31; 86,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,86; 87,51</t>
+          <t>73,96; 87,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,54; 76,78</t>
+          <t>54,1; 76,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,24; 78,29</t>
+          <t>59,03; 77,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,11; 77,87</t>
+          <t>60,05; 77,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,8; 80,94</t>
+          <t>64,6; 79,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,48; 75,74</t>
+          <t>53,13; 75,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,25; 67,76</t>
+          <t>53,6; 67,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,37; 80,33</t>
+          <t>68,07; 79,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,37; 82,46</t>
+          <t>72,18; 81,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,36; 72,98</t>
+          <t>57,59; 72,82</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,02; 65,73</t>
+          <t>49,33; 66,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,63; 74,89</t>
+          <t>58,61; 74,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,9; 79,11</t>
+          <t>62,52; 78,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,3; 84,62</t>
+          <t>57,91; 85,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,33; 64,97</t>
+          <t>48,63; 64,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,02; 78,04</t>
+          <t>62,7; 77,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,89; 75,88</t>
+          <t>57,79; 74,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56,36; 75,05</t>
+          <t>57,67; 75,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,18; 63,22</t>
+          <t>51,04; 62,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64,18; 75,41</t>
+          <t>63,76; 74,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63,97; 75,23</t>
+          <t>63,37; 74,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,43; 78,34</t>
+          <t>60,81; 78,46</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>56,54; 65,37</t>
+          <t>56,86; 65,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,19; 80,25</t>
+          <t>73,15; 80,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,55; 79,69</t>
+          <t>72,64; 79,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,07; 79,5</t>
+          <t>63,53; 79,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,07; 67,54</t>
+          <t>59,33; 68,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,99; 76,6</t>
+          <t>69,4; 76,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,66; 77,22</t>
+          <t>69,4; 77,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>63,54; 75,18</t>
+          <t>64,27; 75,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59,08; 65,36</t>
+          <t>59,25; 65,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72,26; 77,52</t>
+          <t>72,49; 77,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,01; 77,31</t>
+          <t>72,23; 77,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,86; 75,95</t>
+          <t>65,95; 75,52</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22274; 31981</t>
+          <t>22074; 32212</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>61209; 73607</t>
+          <t>60662; 72939</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48695; 60159</t>
+          <t>48303; 59980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10392; 15779</t>
+          <t>10284; 15986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28975; 41014</t>
+          <t>28997; 40533</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60174; 71608</t>
+          <t>58091; 71238</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38954; 49936</t>
+          <t>38949; 49409</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9671; 15246</t>
+          <t>9277; 15046</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54404; 69952</t>
+          <t>54327; 69553</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>124139; 141136</t>
+          <t>125660; 142287</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90314; 106837</t>
+          <t>90848; 107046</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21955; 29649</t>
+          <t>21898; 29869</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60500; 77061</t>
+          <t>61973; 77679</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94656; 111107</t>
+          <t>95475; 110720</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70526; 84679</t>
+          <t>71548; 84119</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32207; 42240</t>
+          <t>31716; 41964</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64849; 79943</t>
+          <t>65049; 80470</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>95590; 113335</t>
+          <t>96423; 114044</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88036; 103160</t>
+          <t>87655; 103340</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43708; 55177</t>
+          <t>44230; 54981</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>130477; 152690</t>
+          <t>129561; 151667</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>196786; 220863</t>
+          <t>197132; 220910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>162581; 183741</t>
+          <t>164012; 183403</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80218; 94696</t>
+          <t>80078; 94508</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32675; 46029</t>
+          <t>33013; 46203</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59561; 72360</t>
+          <t>60206; 72247</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70689; 83753</t>
+          <t>70782; 83612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35336; 50673</t>
+          <t>35705; 50248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33316; 44788</t>
+          <t>33768; 44606</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49264; 62776</t>
+          <t>48411; 62334</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63013; 77505</t>
+          <t>61863; 76353</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34388; 48699</t>
+          <t>34160; 48362</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70142; 87607</t>
+          <t>69303; 87671</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112043; 131639</t>
+          <t>111552; 130954</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138571; 157879</t>
+          <t>138193; 156915</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74745; 95091</t>
+          <t>75034; 94886</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40629; 54474</t>
+          <t>40881; 55337</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54063; 67906</t>
+          <t>53139; 67824</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58253; 73268</t>
+          <t>57905; 73063</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>70918; 104731</t>
+          <t>71670; 105768</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45997; 61838</t>
+          <t>46285; 60990</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68626; 83664</t>
+          <t>67213; 83368</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50027; 64460</t>
+          <t>49097; 63705</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63404; 84424</t>
+          <t>64871; 84392</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91132; 112566</t>
+          <t>90881; 111667</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>126987; 149219</t>
+          <t>126164; 146739</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>113589; 133583</t>
+          <t>112517; 132745</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>142777; 185074</t>
+          <t>143656; 185370</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>170456; 197088</t>
+          <t>171440; 198509</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>284784; 312239</t>
+          <t>284619; 312540</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>262856; 288726</t>
+          <t>263178; 289108</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162495; 204839</t>
+          <t>163670; 205255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>187220; 214065</t>
+          <t>188033; 215929</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>290227; 317646</t>
+          <t>287798; 318138</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>255559; 283291</t>
+          <t>254604; 282717</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>162932; 192773</t>
+          <t>164795; 193078</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>365387; 404206</t>
+          <t>366403; 403945</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>580782; 623064</t>
+          <t>582699; 623538</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>525049; 563719</t>
+          <t>526669; 564503</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>338564; 390416</t>
+          <t>339051; 388210</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP37-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61,68%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>80,02%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>73,8%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>63,98%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>79,87%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>76,06%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>76,86%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>61,68%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>80,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,8%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,89; 75,72</t>
+          <t>51,21; 72,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,68; 86,19</t>
+          <t>72,06; 86,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,14; 83,36</t>
+          <t>64,06; 81,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,66; 91,18</t>
+          <t>52,91; 87,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,17; 71,53</t>
+          <t>51,46; 74,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,16; 86,04</t>
+          <t>72,44; 86,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,36; 81,65</t>
+          <t>66,69; 83,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,03; 86,01</t>
+          <t>57,88; 90,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,76; 70,11</t>
+          <t>53,98; 69,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75,06; 84,99</t>
+          <t>74,26; 84,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68,58; 80,81</t>
+          <t>69,09; 80,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,52; 85,28</t>
+          <t>62,18; 84,33</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>67,45%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>73,15%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>76,4%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81,53%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>66,89%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>79,79%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>76,61%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>74,21%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>67,45%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>73,15%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>76,4%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,23%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,59; 74,69</t>
+          <t>59,92; 74,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,14; 84,82</t>
+          <t>66,16; 79,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,11; 82,42</t>
+          <t>69,85; 81,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,99; 83,34</t>
+          <t>71,02; 88,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,29; 74,59</t>
+          <t>59,14; 73,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,92; 79,15</t>
+          <t>73,39; 85,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,78; 82,27</t>
+          <t>70,08; 82,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,18; 88,48</t>
+          <t>63,1; 83,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61,15; 71,58</t>
+          <t>61,95; 72,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71,78; 80,44</t>
+          <t>71,84; 80,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,04; 80,56</t>
+          <t>71,64; 80,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,19; 84,01</t>
+          <t>70,48; 84,26</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>68,75%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>69,49%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>73,37%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>66,01%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>55,15%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>79,8%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>81,35%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>65,45%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>68,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,37%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>64,23%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45,8; 64,1</t>
+          <t>58,6; 77,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72,31; 86,77</t>
+          <t>60,35; 77,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,96; 87,36</t>
+          <t>64,99; 80,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,1; 76,13</t>
+          <t>54,85; 76,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,03; 77,97</t>
+          <t>45,38; 64,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,05; 77,33</t>
+          <t>71,96; 86,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,6; 79,73</t>
+          <t>73,86; 86,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,13; 75,21</t>
+          <t>52,14; 73,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53,6; 67,81</t>
+          <t>54,41; 68,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,07; 79,91</t>
+          <t>68,93; 79,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,18; 81,95</t>
+          <t>72,0; 82,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,59; 72,82</t>
+          <t>56,25; 71,14</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56,69%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>71,41%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67,79%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64,36%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>57,64%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>67,68%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>71,32%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>69,82%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>56,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>71,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>67,79%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>62,26%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,33; 66,77</t>
+          <t>48,61; 64,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,61; 74,8</t>
+          <t>64,36; 78,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,52; 78,89</t>
+          <t>58,6; 75,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,91; 85,46</t>
+          <t>54,97; 72,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,63; 64,08</t>
+          <t>48,8; 66,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,7; 77,77</t>
+          <t>58,58; 75,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,79; 74,99</t>
+          <t>63,38; 78,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,67; 75,02</t>
+          <t>50,99; 68,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,04; 62,72</t>
+          <t>50,62; 62,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63,76; 74,16</t>
+          <t>64,07; 74,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63,37; 74,76</t>
+          <t>63,95; 75,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,81; 78,46</t>
+          <t>56,01; 68,12</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>73,36%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73,19%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>61,13%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>76,99%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>76,4%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>70,04%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>73,36%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>56,86; 65,84</t>
+          <t>58,76; 67,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,15; 80,32</t>
+          <t>69,75; 76,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,64; 79,79</t>
+          <t>69,34; 76,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,53; 79,67</t>
+          <t>63,97; 74,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,33; 68,13</t>
+          <t>56,86; 66,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,4; 76,72</t>
+          <t>73,46; 80,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,4; 77,07</t>
+          <t>72,36; 79,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,27; 75,3</t>
+          <t>58,93; 69,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59,25; 65,32</t>
+          <t>58,98; 65,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72,49; 77,57</t>
+          <t>72,56; 77,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,23; 77,42</t>
+          <t>72,04; 77,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,95; 75,52</t>
+          <t>63,26; 71,21</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34951</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66253</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44657</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10274</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>27218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>67590</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>54722</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13475</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34951</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66253</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44657</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26325</t>
+          <t>22083</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22074; 32212</t>
+          <t>29022; 40861</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60662; 72939</t>
+          <t>59661; 71702</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48303; 59980</t>
+          <t>38765; 49567</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10284; 15986</t>
+          <t>7547; 12476</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28997; 40533</t>
+          <t>21892; 31542</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58091; 71238</t>
+          <t>61299; 73471</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38949; 49409</t>
+          <t>47986; 60186</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9277; 15046</t>
+          <t>8848; 13823</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54327; 69553</t>
+          <t>53549; 69366</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>125660; 142287</t>
+          <t>124324; 141441</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90848; 107046</t>
+          <t>91521; 107072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21898; 29869</t>
+          <t>18372; 24919</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>123</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72765</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>105394</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>95965</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42981</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>69559</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>104160</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>78182</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37370</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>72765</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>105394</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95965</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50550</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87920</t>
+          <t>77022</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61973; 77679</t>
+          <t>64647; 79847</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95475; 110720</t>
+          <t>95320; 113921</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71548; 84119</t>
+          <t>87745; 102513</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31716; 41964</t>
+          <t>37442; 46827</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65049; 80470</t>
+          <t>61502; 76508</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>96423; 114044</t>
+          <t>95806; 111689</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87655; 103340</t>
+          <t>71522; 84245</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44230; 54981</t>
+          <t>28858; 38072</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>129561; 151667</t>
+          <t>131270; 153825</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>197132; 220910</t>
+          <t>197292; 221157</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>164012; 183403</t>
+          <t>163109; 184302</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80078; 94508</t>
+          <t>69394; 82954</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39331</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56021</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70264</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40703</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>39754</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>66440</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>77857</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>43197</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>39331</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56021</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70264</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42299</t>
+          <t>39732</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85496</t>
+          <t>80435</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33013; 46203</t>
+          <t>33527; 44472</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60206; 72247</t>
+          <t>48646; 62075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70782; 83612</t>
+          <t>62237; 77179</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35705; 50248</t>
+          <t>33821; 47014</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33768; 44606</t>
+          <t>32706; 46471</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48411; 62334</t>
+          <t>59913; 72397</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61863; 76353</t>
+          <t>70690; 83133</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34160; 48362</t>
+          <t>33140; 46659</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69303; 87671</t>
+          <t>70349; 87948</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111552; 130954</t>
+          <t>112952; 130866</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138193; 156915</t>
+          <t>137852; 157598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75034; 94886</t>
+          <t>70438; 89084</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>53952</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>76554</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>57590</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>68498</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>47770</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>61366</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>66053</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>86414</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>53952</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76554</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>57590</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74266</t>
+          <t>59105</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>160681</t>
+          <t>127603</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40881; 55337</t>
+          <t>46266; 61147</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53139; 67824</t>
+          <t>68990; 83848</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57905; 73063</t>
+          <t>49785; 64105</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>71670; 105768</t>
+          <t>58501; 77185</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46285; 60990</t>
+          <t>40440; 55109</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67213; 83368</t>
+          <t>53114; 68205</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49097; 63705</t>
+          <t>58698; 73071</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64871; 84392</t>
+          <t>50234; 67645</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>90881; 111667</t>
+          <t>90124; 110642</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>126164; 146739</t>
+          <t>126774; 147350</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>112517; 132745</t>
+          <t>113553; 134883</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>143656; 185370</t>
+          <t>114792; 139615</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>434</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>214</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>200999</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>304222</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>162456</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>184301</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>299556</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>276814</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>180457</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>200999</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>304222</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>268476</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>179964</t>
+          <t>144687</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>360421</t>
+          <t>307143</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>171440; 198509</t>
+          <t>186230; 213697</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>284619; 312540</t>
+          <t>289252; 319160</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>263178; 289108</t>
+          <t>254378; 281816</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>163670; 205255</t>
+          <t>150383; 175572</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>188033; 215929</t>
+          <t>171439; 199853</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>287798; 318138</t>
+          <t>285815; 312603</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>254604; 282717</t>
+          <t>262174; 289089</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>164795; 193078</t>
+          <t>131478; 155723</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>366403; 403945</t>
+          <t>364768; 404199</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>582699; 623538</t>
+          <t>583210; 621768</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>526669; 564503</t>
+          <t>525292; 563262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>339051; 388210</t>
+          <t>289848; 326240</t>
         </is>
       </c>
     </row>
